--- a/校园招聘/制造业/半导体与集成电路/生产物流类/质量工程师/3_需重新出题/3轮_半导体与集成电路_质量工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/半导体与集成电路/生产物流类/质量工程师/3_需重新出题/3轮_半导体与集成电路_质量工程师_需要重新出题.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chengxi5\Desktop\8月AI审题\半导体与集成电路制造业\质量工程师\3轮审核后需要重出的内容\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/risei/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1EC3CB-4F4C-DC45-B495-4E98E9AE724A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="5530"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="出题" sheetId="1" r:id="rId1"/>
+    <sheet name="出答案" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>问题</t>
   </si>
   <si>
-    <t>第一层</t>
-  </si>
-  <si>
-    <t>第二层</t>
-  </si>
-  <si>
-    <t>第三层</t>
-  </si>
-  <si>
     <t>技能分类</t>
   </si>
   <si>
@@ -63,15 +56,6 @@
     <t>客户审核明确要求调阅某款车规级芯片量产前三个月的出货检验记录及对应批次的可靠性试验报告，但其中两批样品因实验室排期冲突，实际试验完成时间晚于出货日期。你手头有试验委托单、原始测试数据、签发后的报告扫描件，但缺少正式盖章版原件。面对审核员现场索要‘出货前已完成验证’的证据链，你会如何组织现有材料进行合理说明并证明质量受控？</t>
   </si>
   <si>
-    <t>严格依据IATF16949条款8.3.4和8.5.1关于变更控制与放行条件的要求，确认该两批出货已履行特采放行审批流程；同步梳理试验委托单、原始数据、扫描版报告三者之间的批次号、时间戳、责任人签名等关键要素一致性；向审核员清晰说明试验虽滞后完成，但所有验证活动均按APQP阶段计划执行，且结果全部合格。</t>
-  </si>
-  <si>
-    <t>第一种做法是采用‘时间轴+决策链’双线呈现：将出货时间、委托时间、测试启动时间、报告签发时间制成可视化时序图，并附特采评审会议纪要或ECN放行单，适用于审核员关注过程合规性场景；第二种是聚焦证据完整性重构：用原始数据文件属性、电子签名水印、系统日志截图佐证数据真实性和不可篡改性，适合数字审核环境但需提前确认客户接受电子证据；第三种是启用质量协议兜底条款：调取与客户签署的《可靠性验证延迟放行补充协议》或邮件共识记录，最稳妥但依赖前期合同管理成熟度；当前最管用的是第一种，因其兼顾时效性、可追溯性与标准符合性，且无需额外审批。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：审核员认定‘报告未盖章即无效’，拒绝接受扫描件。具体情况：客户质量协议中未明确定义电子版报告效力边界，且部分主机厂仍沿用纸质盖章硬性要求。解决思路：立即提供加盖公司电子签章的PDF报告（符合GB/T 20520-2023电子印章规范），同步出示内部质量系统中该报告的审批流闭环截图及归档路径，强调其与纸质盖章具有同等法律效力。1个复杂问题概要：两批中一批测试结果临界合格，另一批存在一次复测后合格。具体问题：审核员质疑‘出货前未确认最终结论’，动摇质量受控判断。解决思路：调取OQC放行记录中的风险评估表，展示当时基于历史数据、FMEA严重度判定及客户技术代表邮件确认的特采依据，并关联后续所有批次零不良的售后质量数据，用客户实际使用表现反向验证放行决策合理性。</t>
-  </si>
-  <si>
     <t>客户质量管理</t>
   </si>
   <si>
@@ -96,15 +80,6 @@
     <t>某晶圆代工厂向汽车电子客户提交PPAP时，客户退回了全尺寸检验报告，指出报告中仅包含抽样批次的单次测量数据，未体现关键尺寸在整批晶圆上的分布趋势和过程能力指数。你作为质量工程师，需在48小时内完成整改并重新提交。请简述你会优先验证哪些检验数据维度，并说明为什么这些维度对证明量产过程稳定性最关键。</t>
   </si>
   <si>
-    <t>优先验证关键尺寸在整批晶圆上的分布趋势数据、过程能力指数Cpk/Ppk，以及对应测量点在晶圆面内的空间位置映射关系。这三类数据是IATF16949及AIAG PPAP手册中对全尺寸检验报告的核心要求，直接支撑客户对量产过程稳定性和一致性的判定依据。</t>
-  </si>
-  <si>
-    <t>第一种做法是调取该批次SPC历史数据，快速提取近30炉次同关键尺寸的过程能力趋势，适用于已有成熟控制图且数据系统可实时导出的场景；但若当前批次为新工艺或首片验证，则历史数据参考价值有限。第二种做法是基于MES中已采集的该批次全部晶圆实测点位数据，按晶圆号、切片位置、测量点坐标做二维分布热力图+能力值聚合，时效性强且满足汽车客户对空间变异的审查要求；但需确认测量设备已启用自动上传与坐标绑定功能。第三种做法是联合制程与量测工程师，在48小时内补采部分晶圆边缘/中心区域的关键点，结合已有数据插值生成分布趋势；虽能弥补数据缺口，但存在客户质疑补测代表性的风险。当下最管用的是第二种，前提是工厂MES与CD-SEM/AOI量测系统已完成标准化接口对接，可一键生成带空间坐标的全批分布视图。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：客户退回后发现原始量测数据未按晶圆ID及die坐标结构化存储。具体情况是检验报告仅汇总平均值与公差符合性，缺失单点原始数据链路，导致无法回溯分布与能力计算。解决思路是立即启动数据溯源流程，核查量测设备原始输出文件格式与MES入库字段映射关系，临时导出CSV原始数据并人工补录坐标标签，同步推动IT固化‘晶圆ID+场点坐标+实测值’三元组存档规则。1个复杂问题概要：同一关键尺寸在不同晶圆间存在系统性偏移，但单批Cpk达标。具体问题是分布趋势显示前半批偏负、后半批偏正，呈现设备漂移特征，单纯报告Cpk会掩盖过程不稳。解决思路是将分布趋势图与对应光刻/刻蚀机台的PM记录、气体流量监控曲线做时间轴对齐分析，识别潜在设备状态关联性，并在整改报告中增加‘趋势稳定性说明’段落，明确标注是否已触发SPC再确认动作。</t>
-  </si>
-  <si>
     <t>新产品质量策划</t>
   </si>
   <si>
@@ -117,15 +92,6 @@
     <t>在开展半导体封装过程审核时，发现引线键合工序的设备OEE数据稳定在92%，但同期该工序的客户投诉中焊点虚焊占比达45%。你认为仅凭OEE数据能否证明该过程受控？请简述应核查哪些过程绩效证据来验证真实过程能力，并说明它们如何共同支撑过程稳定性判断。</t>
   </si>
   <si>
-    <t>不能仅凭OEE数据证明该过程受控。OEE反映设备可用性、性能率和合格率的综合效率，但其合格率子项通常基于在线目检或简单电测判定的‘可放行品’，无法等同于客户关注的焊点结构完整性与长期可靠性。过程受控需以客户关注的关键质量特性为基准，通过多维过程绩效证据交叉验证真实的过程能力与稳定性。</t>
-  </si>
-  <si>
-    <t>首先应核查SPC控制图中引线键合关键参数（如键合力、弧高、焊点形貌图像识别得分）的统计受控状态，该方法对早期微小漂移敏感，但若取样频次低或测量系统未校准则易漏判；其次调取近3个月该工序的FTIR/ICT/SLT测试一次通过率及分层缺陷TOP分析，能定位虚焊是否集中于特定产品型号或批次，但若测试覆盖率不足或失效复现机制缺失则结论偏颇；再查控制计划执行记录与IPQC巡检数据的一致性，可验证标准落地有效性，但若检查表未覆盖虚焊关键诱因（如金线张力波动、劈刀磨损记录）则流于形式；最后比对客户退回样品FA报告与内部过程数据的关联性，是闭环验证的黄金证据，但需确保FA结果及时反哺过程监控项。当前最管用的是将SPC趋势与客户FA焊点金相分析结果做时间轴对齐，快速锁定过程变异窗口。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：SPC控制图显示键合力均值稳定，但客户FA确认虚焊主因是第二焊点IMC层不连续。具体情况是过程监控仅设定了键合力上下限，未将IMC生长质量纳入关键控制特性，导致监控盲区。解决思路是立即修订控制计划，将超声能量积分值与键合后AOI焊点灰度一致性纳入SPC监控，并同步更新IPQC检验要点。1个复杂问题概要：多个产品共用同一键合设备，不同产品焊点尺寸差异大，但OEE合格率统一按‘无开路’统计。具体问题是现有过程绩效证据未按产品族分层建模，无法识别某类小焊盘产品虚焊率持续超标。解决思路是推动建立产品维度的过程能力看板，按封装类型、焊点尺寸段分别统计CPK与虚焊PPM，并与客户投诉数据自动映射，实现风险精准预警。</t>
-  </si>
-  <si>
     <t>质量体系审核</t>
   </si>
   <si>
@@ -133,21 +99,139 @@
   </si>
   <si>
     <t>过程绩效证据</t>
-  </si>
-  <si>
-    <t>禁止要求证明/推导/公式书写/图表绘制/书面报告附件；题干必须可在2-3分钟口述回答；场景限定为质量工程师高频业务（来料/过程/出货/客诉闭环、SPC、8D、MSA、失效分析），避免偏门场景。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1) 先给岗位口径定义与判定标准；2) 再给可执行步骤与先后顺序；3) 明确关键指标、阈值或记录要求来源；4) 补充1个常见异常与1个复杂问题及纠偏策略。禁止把假设值当标准结论，禁止与题干知识点不一致的扩展。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一、制程质量监控与过程能力管理
+负责晶圆制造、封装测试、半导体材料或器件量产过程中的质量监控，跟踪关键质量指标和关键工艺特性，识别SPC异常、不良率波动、过程能力不足等风险；校招/初级可参与数据收集、趋势判断和异常跟进，3-5年经验需能独立推动过程质量分析、控制计划维护和过程能力改善。
+二、质量异常分析与闭环改善
+负责生产异常、来料异常、出货异常、客诉异常和可靠性异常的调查分析，运用系统化问题解决方法定位根因，制定纠正预防措施并验证改善效果；初级侧重参与8D资料整理和单点异常跟进，3-5年经验需能主导中等复杂度异常闭环，沉淀防再发机制。
+三、良率提升与质量改进项目
+围绕晶圆制造、封装、测试或半导体材料生产中的良率、DPPM、PPM、客诉率、报废率等指标，分析质量数据和缺陷分布，识别关键瓶颈，推动质量改进项目并跟踪改善成效；校招/初级偏基础数据分析和改善验证，3-5年经验需能独立设计改善思路并推动项目闭环。
+四、新产品导入与质量策划
+参与新材料、新工艺、新产品或研发转量产阶段的质量策划，识别质量风险，制定检验标准、控制计划、可靠性验证计划和阶段评审要求，确保研发样品、试生产、量产爬坡过程质量受控；3-5年经验需能主导APQP/PPAP/OTS等阶段性质量交付和风险评审。
+五、来料与供应商质量管理
+负责晶圆、封测服务、半导体材料、关键零部件或外协加工的质量准入、来料检验、供应商异常处理和改善追踪；初级可参与来料异常记录和检验标准执行，3-5年经验需能开展供应商过程审核、来料风险评估和供应商质量改善闭环。
+六、客户质量与出货质量管理
+负责客户投诉、客户审核、出货检验标准、质量月报和客户端质量数据分析，推动内部质量问题闭环并降低客诉率；初级可参与信息收集和8D资料整理，3-5年经验需能独立进行客诉调查、客户质量报告输出和审核应对。
+七、失效分析与可靠性验证
+针对芯片、晶圆、封装件、功率器件、硅材料或半导体元器件的失效问题，参与电性确认、结构/材料分析、失效根因定位和可靠性验证计划执行；校招/初级需理解常见失效现象和基础测试逻辑，3-5年经验需能结合FA结果推动制程或设计改善。
+八、质量体系运行与审核改善
+参与或负责ISO9001、IATF16949、QC080000、VDA6.3/VDA6.5等质量体系在半导体制造/封测/材料场景中的落地，推动内审、过程审核、产品审核、体系整改和质量流程优化；初级偏体系资料维护和审核问题跟进，5年左右需能独立推动体系审核和质量流程建设。
+九、检验标准与质量文件管理
+制定、更新和维护IQC、IPQC、OQC、SIP、SOP、控制计划、检验规范和质量记录要求，确保质量判定标准清晰、过程执行一致、异常可追溯；初级偏执行和维护，3-5年经验需能根据异常和变更更新标准并验证执行效果。
+十、变更质量与风险预防管理
+负责或参与PCN/ECN、工艺变更、材料变更、供应商变更、量产初期管理和客户变更要求评审，识别变更对质量、可靠性和交付风险的影响，并制定验证与放行条件；3-5年经验需能独立组织变更风险评审和验证闭环。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为【{{industry}}】行业下的【{{job}}】岗位的候选人精心准备【{{num}}】道视频面试题。
+关于目标行业下岗位的岗位描述：【{{JD}}】
+## 面试题要求
+- 题目类型：必须为简答题。
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 行业岗位适用性：题目需与【{{industry}}】行业下的【{{job}}】岗位职责高度适配，贴合该行业实际情况。
+- 招聘场景：题目应契合【{{scene}}】这一特定招聘场景。
+- 题目难度：全部设定为【{{level}}】难度，具体难度定义如下：
+    · 简单：考察应聘者能否正确识别、描述生产物流中常见的业务流程、术语和操作规范，是否清楚这些操作背后的基本逻辑。提问内容涉及流程认知与业务常识，无场景，纯基础考察。例如要求复述某类物料的出入库操作要点或解释某个作业术语的含义，如“先进先出原则在仓库中如何体现？”。建议作答时间控制在60秒内。字数控制在10～30字。
+    · 中等：考察应聘者是否知道在一个常规生产或仓储作业场景下，用何种方法处理异常或改善现状，解决机制是什么。提问内容涉及操作方法的实际运用，场景是日常工作中会遇到的典型情况，禁止涉及穷举、优劣势分析、系统性设计或冲突情况。如“当生产线的物料配送出现积压，导致线边仓爆满影响现场6S和作业动线时，你会怎么调整配送节拍或叫料方式来解决？”建议作答时间控制在90秒内。字数控制在30～60字。
+    · 困难：考察应聘者在复杂业务场景下的判断力和统筹能力。提问内容是一个具体的、两难的生产或物流局面，需要候选人说清楚先保什么、放什么，凭什么这么取舍，事后怎么收场。场景是车间或仓库里真实会发生的复杂情景。如“产线上正在跑的A产品突然要加大产量，但备好的料是按原计划供的，这时候插单和缺料的压力全压在了现场。你会从哪几个环节动手，怎么调整才能稳住交期又不让库存冒顶？说说你的思路和先动哪步后动哪步的理由。”建议作答时间控制在120秒内。字数控制在60～90字。
+- 题干长度：一个题目里只能有1个小问，禁止连环提问！使读题时间控制在30秒内，难度越低的题题干应越好理解。
+-易答性：
+1.禁用词：写代码、写出、编写、绘制、计算等一些口头无法表述的内容，确保候选人仅通过口头回答即可完成答题；
+2.不能出现让候选人讲述某一个软件的操作步骤；
+3.提问应该逻辑严谨，简单易懂，提出问题时需要模仿面试官在面试的口吻，不能过于生硬而让候选人不能明白题目的意思；
+4.编程题要给出规定的编程语言。
+- 特别注意：禁止要求证明/推导/公式书写/图表绘制/书面报告附件；题干必须可在2-3分钟口述回答；场景限定为质量工程师高频业务（来料/过程/出货/客诉闭环、SPC、8D、MSA、失效分析），避免偏门场景。
+- 内容限制：
+1.问题中的应用场景/条件不能是虚构的或者故事化的场景。语言上，类似“假设....”的提问是不被允许的。
+2.技术时效性：题干禁止问旧版本/早期版本的技术，涉及的技术场景必须是2022年之后在用的，但不必在题干中标注年份。
+3.问题中不能出现【{{industry}}】行业名称、【{{scene}}】特定招聘场景名称、【{{job}}】职位
+4.对于【通用行业】的知识点提问需要通用化，业务场景需要是各行各业的应聘者都能看懂的。
+5.所有的问题都是知识点面试问题，不能出行为化面试题
+6.尽量不要出现英文，能用中文的用中文表达！
+7.禁止出现事实、知识错误！
+8.禁止出现“请用一句话回答”这类强势粗暴的提问方法，可以说“请简述”“请简单说说”等
+## 输出规范要求
+- 若题目数量超过 1 道，要保证所有题目内容不重复，从不同主题或提问角度进行设计。
+- 严格以规范的 JSON 格式输出结果，不包含任何额外的文本说明。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""level"": ""难度"",
+        ""time"": 建议答题时间，整数类型
+    }}]
+}}"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"一、制程质量监控与过程能力管理
+负责晶圆制造、封装测试、半导体材料或器件量产过程中的质量监控，跟踪关键质量指标和关键工艺特性，识别SPC异常、不良率波动、过程能力不足等风险；校招/初级可参与数据收集、趋势判断和异常跟进，3-5年经验需能独立推动过程质量分析、控制计划维护和过程能力改善。
+二、质量异常分析与闭环改善
+负责生产异常、来料异常、出货异常、客诉异常和可靠性异常的调查分析，运用系统化问题解决方法定位根因，制定纠正预防措施并验证改善效果；初级侧重参与8D资料整理和单点异常跟进，3-5年经验需能主导中等复杂度异常闭环，沉淀防再发机制。
+三、良率提升与质量改进项目
+围绕晶圆制造、封装、测试或半导体材料生产中的良率、DPPM、PPM、客诉率、报废率等指标，分析质量数据和缺陷分布，识别关键瓶颈，推动质量改进项目并跟踪改善成效；校招/初级偏基础数据分析和改善验证，3-5年经验需能独立设计改善思路并推动项目闭环。
+四、新产品导入与质量策划
+参与新材料、新工艺、新产品或研发转量产阶段的质量策划，识别质量风险，制定检验标准、控制计划、可靠性验证计划和阶段评审要求，确保研发样品、试生产、量产爬坡过程质量受控；3-5年经验需能主导APQP/PPAP/OTS等阶段性质量交付和风险评审。
+五、来料与供应商质量管理
+负责晶圆、封测服务、半导体材料、关键零部件或外协加工的质量准入、来料检验、供应商异常处理和改善追踪；初级可参与来料异常记录和检验标准执行，3-5年经验需能开展供应商过程审核、来料风险评估和供应商质量改善闭环。
+六、客户质量与出货质量管理
+负责客户投诉、客户审核、出货检验标准、质量月报和客户端质量数据分析，推动内部质量问题闭环并降低客诉率；初级可参与信息收集和8D资料整理，3-5年经验需能独立进行客诉调查、客户质量报告输出和审核应对。
+七、失效分析与可靠性验证
+针对芯片、晶圆、封装件、功率器件、硅材料或半导体元器件的失效问题，参与电性确认、结构/材料分析、失效根因定位和可靠性验证计划执行；校招/初级需理解常见失效现象和基础测试逻辑，3-5年经验需能结合FA结果推动制程或设计改善。
+八、质量体系运行与审核改善
+参与或负责ISO9001、IATF16949、QC080000、VDA6.3/VDA6.5等质量体系在半导体制造/封测/材料场景中的落地，推动内审、过程审核、产品审核、体系整改和质量流程优化；初级偏体系资料维护和审核问题跟进，5年左右需能独立推动体系审核和质量流程建设。
+九、检验标准与质量文件管理
+制定、更新和维护IQC、IPQC、OQC、SIP、SOP、控制计划、检验规范和质量记录要求，确保质量判定标准清晰、过程执行一致、异常可追溯；初级偏执行和维护，3-5年经验需能根据异常和变更更新标准并验证执行效果。
+十、变更质量与风险预防管理
+负责或参与PCN/ECN、工艺变更、材料变更、供应商变更、量产初期管理和客户变更要求评审，识别变更对质量、可靠性和交付风险的影响，并制定验证与放行条件；3-5年经验需能独立组织变更风险评审和验证闭环。"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为面试【{{job}}】职位的候选人的视频面试题【{{Q}}】生成符合规则的参考答案。
+## 参考答案要求
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 岗位适用性：答案需与【{{{industry}}】行业的【{{job}}】岗位的工作范畴高度适配，仅从该岗位工作内容角度生成。禁止从技术的口径回答问题！！岗位工作内容参考：【{{JD}}】
+- 使用场景：答案应契合【{{scene}}】这一特定使用场景。
+- 内容与格式：每个题目的三层参考答案字数合计限制在300～600字，每个题目考察的都是一个岗位上某个技能的掌握程度，掌握程度分为三个层次，因此参考答案也需要分层生成。对第一层给出回答题干所需的基本操作要点、流程要求或业务常识}，内容严格对应题干，不要举例，不要超出题干所问的范围！对第二层给出给出这个场景下常见实用的2～4种作业方法或调整套路的分析，每种做法在什么情况下好用、什么情况下会出问题，哪种在当下最管用，方法要在保证时效性的基础上全面！分析要深入！对第三层给出这个知识点或场景下最最常出现的1个异常情况和1个复杂问题，以及每种情况的解决思路，输出时要结构化！小标题结构为：1个异常情况概要，具体情况，解决思路；1个复杂问题概要，具体问题，解决思路。
+参考答案约束：
+1.参考答案的内容必须严格对应岗位口径
+2.禁止出现代码块、符号等书面表达，所有类似内容必须用口语自然语言描述的形式代替
+3.禁止出现公式、计算等
+4.能用中文的用中文表达
+5.涉及的技术方法必须是2023年之后在用的，但相关时间信息不必出现在答案文本中
+6.禁止出现知识、事实错误！！
+常见的错误清单：{把相近概念混为一谈
+把局部实现写成通用规律
+把适用条件说错或漏掉前提
+把可选方案写成唯一答案
+数学/统计结论直接上升为业务结论
+边界值、分类、覆盖率类题目只答一半
+举例本身错误
+绝对化、法条化、一刀切表述}
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+          ""answer1"":""参考答案-第一层"",
+          ""answer2"":""参考答案-第二层"",
+          ""answer3"":""参考答案-第三层""
+    }}]
+}}"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +243,21 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -183,8 +282,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -486,11 +591,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,125 +626,98 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="409.6">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11" ht="409.6">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="409.6">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="N2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -647,4 +725,31 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FC777D-4EA1-FD44-8AED-78805F9112B5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>